--- a/DXLibProject_Start/Data/CSV/EnemyModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/EnemyModel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB5869-2849-4FB3-BE59-68C8F08DD5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320E217D-B9D6-4241-BF23-89E82B73B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2655" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerModelPath" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -86,10 +87,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>Dead.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>Idle</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -139,6 +136,10 @@
   </si>
   <si>
     <t>Resource\\Enemy\\Queen\\</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Death.mv1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -805,9 +806,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -845,7 +846,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -951,7 +952,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1093,7 +1094,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1133,15 +1134,15 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" t="s">
         <v>26</v>
-      </c>
-      <c r="K1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1157,22 +1158,22 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1190,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1197,7 +1198,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1213,7 +1214,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1221,7 +1222,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1237,7 +1238,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>6</v>

--- a/DXLibProject_Start/Data/CSV/EnemyModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/EnemyModel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320E217D-B9D6-4241-BF23-89E82B73B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3759BDE-39B9-44DB-BB10-40EA5B22BC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2655" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,88 +58,88 @@
     <t>animPath[4]</t>
   </si>
   <si>
+    <t>Model.mv1</t>
+  </si>
+  <si>
+    <t>Idle.mv1</t>
+  </si>
+  <si>
+    <t>animPath[1]</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>animNum</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Max</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Walk</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Idle</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Roar</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Run</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>JumpAttack</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Death</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Roar.mv1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Walk.mv1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Run.mv1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>JumpAttack.mv1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Damage.mv1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>animPath[5]</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>animPath[6]</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Resource\\Enemy\\Queen\\</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Death.mv1</t>
+  </si>
+  <si>
     <t>Motions\\</t>
-  </si>
-  <si>
-    <t>Model.mv1</t>
-  </si>
-  <si>
-    <t>Idle.mv1</t>
-  </si>
-  <si>
-    <t>animPath[1]</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>animNum</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Max</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Walk</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Idle</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Roar</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Run</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>JumpAttack</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Death</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Roar.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Walk.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Run.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>JumpAttack.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Damage.mv1</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>animPath[5]</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>animPath[6]</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Resource\\Enemy\\Queen\\</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Death.mv1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1104,6 +1104,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1116,13 +1126,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -1134,46 +1144,46 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
         <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2">
         <f>status!B8</f>
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1200,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1198,7 +1208,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1206,7 +1216,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1214,7 +1224,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1222,7 +1232,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1230,7 +1240,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1238,7 +1248,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1246,7 +1256,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>7</v>
